--- a/docs/downloads/20260812_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260812_Johor_Teduh_Weekly_Update.xlsx
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>416</v>
+        <v>1500</v>
       </c>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="11" t="n">
